--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Anaïs attend encore. Puis la maîtresse dit : Anaïs, c'est ton tour. Anaïs parle. Elle dit : le chat est gris. La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande. Anaïs dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
+          <t>Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Anaïs attend encore. Puis Anaïs, c'est ton tour. Anaïs parle. Le chat est gris. La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Anaïs attend encore. Puis
+maitresse|Anaïs, c'est ton tour.
+narrateur|Anaïs parle.
+narrateur|Le chat est gris.
+narrateur|La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande.
+enfant-f|J'ai levé la main. J'ai su attendre.
+narrateur|Puis parler, c'était mon tour.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs a levé la main. Elle a attendu. Puis parler, c'était son tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs range son cartable. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis parler, c'était mon tour.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Anaïs veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Anaïs a levé la main. Elle a attendu. Puis parler, c'était son tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Anaïs range son cartable. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anaïs attend son tour de parole</t>
+          <t>Le poisson orange de Mila</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COL.POL.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila dessine une maison sur la vitre embuée. En classe, le poisson orange nage dans le bocal. Elle lève la main. Elle attend. Puis elle parle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Anaïs attend encore. Puis Anaïs, c'est ton tour. Anaïs parle. Le chat est gris. La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
+          <t>La vitre de la cuisine est toute embuée. Mila dessine une petite maison du bout du doigt. Une goutte glisse sur le toit dessiné. Tu as fait une fenêtre. Elle est ronde. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est dans ta poche. Tu l'as senti ? Oui. Il est lisse. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent au plafond. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. Bravo. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste dans sa poche. Le poisson du bocal fait un petit tour. Bonjour les enfants. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson du bocal est orange et calme. Elle lève la main. Elle attend. Un camarade parle d'abord d'une barque en papier. Mila attend encore, la main haute. Elle regarde un poisson en papier qui tourne. Mila, c'est ton tour. Tu peux parler. Le poisson du bocal est orange. Il nage tout doucement. Merci, Mila. Tu as attendu. Puis tu as parlé. C'est du bon travail. Plus tard, Mila a encore une idée. Elle lève la main. Elle attend. Mila, c'est encore ton tour. Les poissons en papier nagent aussi, un peu. Oui. Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Anaïs attend encore. Puis
-maitresse|Anaïs, c'est ton tour.
-narrateur|Anaïs parle.
-narrateur|Le chat est gris.
-narrateur|La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande.
-enfant-f|J'ai levé la main. J'ai su attendre.
-narrateur|Puis parler, c'était mon tour.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|Mila dessine une petite maison du bout du doigt.
+narrateur|Une goutte glisse sur le toit dessiné.
+maman|Tu as fait une fenêtre. Elle est ronde.
+papa|Tes bottes rouges attendent sur le paillasson.
+enfant-f|Elles sont un peu froides.
+papa|On les enfile. Une. Puis l'autre.
+maman|Le crayon bleu est dans ta poche. Tu l'as senti ?
+enfant-f|Oui. Il est lisse.
+narrateur|Dehors, le brouillard sent l'herbe mouillée.
+narrateur|Les bottes font un bruit mou sur le chemin.
+papa|On tient la main. Le chemin est encore gris.
+narrateur|Dans la classe, des poissons en papier pendent au plafond.
+narrateur|Ils bougent un peu, tout doucement.
+narrateur|Un bocal rond brille près de la fenêtre.
+maman|Le tapis rond est à ta place, Mila.
+maman|Au revoir. On revient te chercher.
+enfant-f|Au revoir, maman.
+papa|Tu poses le sac près du mur. Bravo.
+narrateur|En ce moment, Mila s'assoit sur le tapis rond.
+narrateur|Le crayon bleu reste dans sa poche.
+narrateur|Le poisson du bocal fait un petit tour.
+maitresse|Bonjour les enfants.
+enfant-f|Bonjour.
+maitresse|Qui a vu quelque chose qui nage ?
+narrateur|Mila a une idée.
+narrateur|Le poisson du bocal est orange et calme.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+narrateur|Un camarade parle d'abord d'une barque en papier.
+narrateur|Mila attend encore, la main haute.
+narrateur|Elle regarde un poisson en papier qui tourne.
+maitresse|Mila, c'est ton tour.
+maitresse|Tu peux parler.
+enfant-f|Le poisson du bocal est orange.
+enfant-f|Il nage tout doucement.
+maitresse|Merci, Mila. Tu as attendu. Puis tu as parlé.
+maitresse|C'est du bon travail.
+narrateur|Plus tard, Mila a encore une idée.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maitresse|Mila, c'est encore ton tour.
+enfant-f|Les poissons en papier nagent aussi, un peu.
+maitresse|Oui. Tu as attendu. Puis tu as parlé.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pas,eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Anaïs veut parler. Que fait-elle d'abord ?</t>
+          <t>Mila veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs veut parler. Que fait-elle d'abord ?</t>
+          <t>narrateur|Mila veut parler.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Anaïs a levé la main. Elle a attendu. Puis parler, c'était son tour.</t>
+          <t>Mila a levé la main. Elle a attendu. Puis parler, c'était son tour. Tu as levé la main. Bravo. Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1733,11 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs a levé la main. Elle a attendu. Puis parler, c'était son tour.</t>
+          <t>narrateur|Mila a levé la main.
+narrateur|Elle a attendu.
+narrateur|Puis parler, c'était son tour.
+maitresse|Tu as levé la main. Bravo.
+maitresse|Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Anaïs range son cartable. Maman l'attend à la porte.</t>
+          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. Maman attend près de la porte. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé du poisson ? Oui. Il est orange. Bravo, Mila. Tu as fait du bon travail. Le brouillard est parti. On rentre. La vitre de la cuisine est sèche. La petite maison du doigt n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1901,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs range son cartable. Maman l'attend à la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Plus tard, Mila range son cartable.
+narrateur|Le crayon bleu est encore dans sa poche.
+narrateur|Maman attend près de la porte.
+maman|Tu as passé un bon moment ?
+enfant-f|J'ai levé la main.
+enfant-f|J'ai su attendre.
+enfant-f|Puis parler, c'était mon tour.
+papa|Tu as parlé du poisson ?
+enfant-f|Oui. Il est orange.
+maman|Bravo, Mila. Tu as fait du bon travail.
+papa|Le brouillard est parti. On rentre.
+narrateur|La vitre de la cuisine est sèche.
+narrateur|La petite maison du doigt n'est plus là.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les bottes rouges sèchent sur le paillasson. Tu as attendu. Puis tu as parlé. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2085,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les bottes rouges sèchent sur le paillasson.
+papa|Tu as attendu. Puis tu as parlé.
+maman|Bonne soirée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -1332,22 +1332,30 @@
           <t>narrateur|La vitre de la cuisine est toute embuée.
 narrateur|Mila dessine une petite maison du bout du doigt.
 narrateur|Une goutte glisse sur le toit dessiné.
-maman|Tu as fait une fenêtre. Elle est ronde.
+maman|Tu as fait une fenêtre.
+maman|Elle est ronde.
 papa|Tes bottes rouges attendent sur le paillasson.
 enfant-f|Elles sont un peu froides.
-papa|On les enfile. Une. Puis l'autre.
-maman|Le crayon bleu est dans ta poche. Tu l'as senti ?
-enfant-f|Oui. Il est lisse.
+papa|On les enfile.
+papa|Une.
+papa|Puis l'autre.
+maman|Le crayon bleu est dans ta poche.
+maman|Tu l'as senti ?
+enfant-f|Oui.
+enfant-f|Il est lisse.
 narrateur|Dehors, le brouillard sent l'herbe mouillée.
 narrateur|Les bottes font un bruit mou sur le chemin.
-papa|On tient la main. Le chemin est encore gris.
+papa|On tient la main.
+papa|Le chemin est encore gris.
 narrateur|Dans la classe, des poissons en papier pendent au plafond.
 narrateur|Ils bougent un peu, tout doucement.
 narrateur|Un bocal rond brille près de la fenêtre.
 maman|Le tapis rond est à ta place, Mila.
-maman|Au revoir. On revient te chercher.
+maman|Au revoir.
+maman|On revient te chercher.
 enfant-f|Au revoir, maman.
-papa|Tu poses le sac près du mur. Bravo.
+papa|Tu poses le sac près du mur.
+papa|Bravo.
 narrateur|En ce moment, Mila s'assoit sur le tapis rond.
 narrateur|Le crayon bleu reste dans sa poche.
 narrateur|Le poisson du bocal fait un petit tour.
@@ -1365,14 +1373,18 @@
 maitresse|Tu peux parler.
 enfant-f|Le poisson du bocal est orange.
 enfant-f|Il nage tout doucement.
-maitresse|Merci, Mila. Tu as attendu. Puis tu as parlé.
+maitresse|Merci, Mila.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.
 maitresse|C'est du bon travail.
 narrateur|Plus tard, Mila a encore une idée.
 narrateur|Elle lève la main.
 narrateur|Elle attend.
 maitresse|Mila, c'est encore ton tour.
 enfant-f|Les poissons en papier nagent aussi, un peu.
-maitresse|Oui. Tu as attendu. Puis tu as parlé.</t>
+maitresse|Oui.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1736,8 +1748,10 @@
           <t>narrateur|Mila a levé la main.
 narrateur|Elle a attendu.
 narrateur|Puis parler, c'était son tour.
-maitresse|Tu as levé la main. Bravo.
-maitresse|Tu as attendu. Puis tu as parlé.</t>
+maitresse|Tu as levé la main.
+maitresse|Bravo.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1765,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. Maman attend près de la porte. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé du poisson ? Oui. Il est orange. Bravo, Mila. Tu as fait du bon travail. Le brouillard est parti. On rentre. La vitre de la cuisine est sèche. La petite maison du doigt n'est plus là.</t>
+          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé du poisson ? Oui. Il est orange. Bravo, Mila. Tu as fait du bon travail. Le brouillard est parti. On rentre. La vitre de la cuisine est sèche. La petite maison du doigt n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1903,15 +1917,18 @@
         <is>
           <t>narrateur|Plus tard, Mila range son cartable.
 narrateur|Le crayon bleu est encore dans sa poche.
-narrateur|Maman attend près de la porte.
+narrateur|La porte s'ouvre.
 maman|Tu as passé un bon moment ?
 enfant-f|J'ai levé la main.
 enfant-f|J'ai su attendre.
 enfant-f|Puis parler, c'était mon tour.
 papa|Tu as parlé du poisson ?
-enfant-f|Oui. Il est orange.
-maman|Bravo, Mila. Tu as fait du bon travail.
-papa|Le brouillard est parti. On rentre.
+enfant-f|Oui.
+enfant-f|Il est orange.
+maman|Bravo, Mila.
+maman|Tu as fait du bon travail.
+papa|Le brouillard est parti.
+papa|On rentre.
 narrateur|La vitre de la cuisine est sèche.
 narrateur|La petite maison du doigt n'est plus là.</t>
         </is>
@@ -2086,7 +2103,8 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Les bottes rouges sèchent sur le paillasson.
-papa|Tu as attendu. Puis tu as parlé.
+papa|Tu as attendu.
+papa|Puis tu as parlé.
 maman|Bonne soirée, ma grande.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2110,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2171,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le poisson orange de Mila</t>
+          <t>Le poisson derrière la plante</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>classe</t>
+          <t>cour à l'arrosoir, puis classe au bocal</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anaïs, maman, maîtresse</t>
+          <t>Mila, papa, maman, maîtresse</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila dessine une maison sur la vitre embuée. En classe, le poisson orange nage dans le bocal. Elle lève la main. Elle attend. Puis elle parle.</t>
+          <t>Mila veut revoir le poisson orange derrière la plante. Le mot est déjà là. Elle lève la main, elle attend, puis elle parle.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute embuée. Mila dessine une petite maison du bout du doigt. Une goutte glisse sur le toit dessiné. Tu as fait une fenêtre. Elle est ronde. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est dans ta poche. Tu l'as senti ? Oui. Il est lisse. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent au plafond. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. Bravo. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste dans sa poche. Le poisson du bocal fait un petit tour. Bonjour les enfants. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson du bocal est orange et calme. Elle lève la main. Elle attend. Un camarade parle d'abord d'une barque en papier. Mila attend encore, la main haute. Elle regarde un poisson en papier qui tourne. Mila, c'est ton tour. Tu peux parler. Le poisson du bocal est orange. Il nage tout doucement. Merci, Mila. Tu as attendu. Puis tu as parlé. C'est du bon travail. Plus tard, Mila a encore une idée. Elle lève la main. Elle attend. Mila, c'est encore ton tour. Les poissons en papier nagent aussi, un peu. Oui. Tu as attendu. Puis tu as parlé.</t>
+          <t>L'arrosoir de la cour a une goutte au bec. La goutte tombe sur la dalle. Un petit serpent d'eau brille, puis s'arrête. Le yaourt de Mila a un fil de miel. Le miel fait un pont, tu vois ? Il est tout doré. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est derrière ton oreille. Tu l'as senti ? Oui. Il est lisse. Tu voulais revoir le poisson, ce matin. Celui qui se cache. Derrière la plante. Tu le raconteras, si tu veux. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste derrière son oreille. Le poisson du bocal fait un petit tour. Il passe derrière la plante verte. Il est encore là. Bonjour. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson orange derrière la plante. Le mot est déjà là. Elle avance un peu les lèvres. La maîtresse verse encore des graines dans le bocal. Les graines font un tout petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Anaïs attend encore. Puis la maîtresse dit : Anaïs, c'est ton tour. Anaïs parle. Elle dit : le chat est gris. La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande. Anaïs dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir de la cour a une goutte au bec. La goutte tombe sur la dalle. Un petit serpent d'eau brille, puis s'arrête. Le yaourt de Mila a un fil de miel. Le miel fait un pont, tu vois ? Il est tout doré. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est derrière ton oreille. Tu l'as senti ? Oui. Il est lisse. Tu voulais revoir le poisson, ce matin. Celui qui se cache. Derrière la plante. Tu le raconteras, si tu veux. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste derrière son oreille. Le poisson du bocal fait un petit tour. Il passe derrière la plante verte. Il est encore là. Bonjour. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson orange derrière la plante. Le mot est déjà là. Elle avance un peu les lèvres. La maîtresse verse encore des graines dans le bocal. Les graines font un tout petit bruit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,25 +1329,30 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vitre de la cuisine est toute embuée.
-narrateur|Mila dessine une petite maison du bout du doigt.
-narrateur|Une goutte glisse sur le toit dessiné.
-maman|Tu as fait une fenêtre.
-maman|Elle est ronde.
+          <t>narrateur|L'arrosoir de la cour a une goutte au bec.
+narrateur|La goutte tombe sur la dalle.
+narrateur|Un petit serpent d'eau brille, puis s'arrête.
+narrateur|Le yaourt de Mila a un fil de miel.
+maman|Le miel fait un pont, tu vois ?
+enfant-f|Il est tout doré.
 papa|Tes bottes rouges attendent sur le paillasson.
-enfant-f|Elles sont un peu froides.
-papa|On les enfile.
+papa|Elles sont un peu froides.
+enfant-f|On les enfile.
 papa|Une.
 papa|Puis l'autre.
-maman|Le crayon bleu est dans ta poche.
+maman|Le crayon bleu est derrière ton oreille.
 maman|Tu l'as senti ?
 enfant-f|Oui.
 enfant-f|Il est lisse.
+papa|Tu voulais revoir le poisson, ce matin.
+enfant-f|Celui qui se cache.
+enfant-f|Derrière la plante.
+maman|Tu le raconteras, si tu veux.
 narrateur|Dehors, le brouillard sent l'herbe mouillée.
 narrateur|Les bottes font un bruit mou sur le chemin.
 papa|On tient la main.
 papa|Le chemin est encore gris.
-narrateur|Dans la classe, des poissons en papier pendent au plafond.
+narrateur|Dans la classe, des poissons en papier pendent.
 narrateur|Ils bougent un peu, tout doucement.
 narrateur|Un bocal rond brille près de la fenêtre.
 maman|Le tapis rond est à ta place, Mila.
@@ -1355,41 +1360,25 @@
 maman|On revient te chercher.
 enfant-f|Au revoir, maman.
 papa|Tu poses le sac près du mur.
-papa|Bravo.
 narrateur|En ce moment, Mila s'assoit sur le tapis rond.
-narrateur|Le crayon bleu reste dans sa poche.
+narrateur|Le crayon bleu reste derrière son oreille.
 narrateur|Le poisson du bocal fait un petit tour.
-maitresse|Bonjour les enfants.
+narrateur|Il passe derrière la plante verte.
+enfant-f|Il est encore là.
+maitresse|Bonjour.
 enfant-f|Bonjour.
 maitresse|Qui a vu quelque chose qui nage ?
 narrateur|Mila a une idée.
-narrateur|Le poisson du bocal est orange et calme.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-narrateur|Un camarade parle d'abord d'une barque en papier.
-narrateur|Mila attend encore, la main haute.
-narrateur|Elle regarde un poisson en papier qui tourne.
-maitresse|Mila, c'est ton tour.
-maitresse|Tu peux parler.
-enfant-f|Le poisson du bocal est orange.
-enfant-f|Il nage tout doucement.
-maitresse|Merci, Mila.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.
-maitresse|C'est du bon travail.
-narrateur|Plus tard, Mila a encore une idée.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-maitresse|Mila, c'est encore ton tour.
-enfant-f|Les poissons en papier nagent aussi, un peu.
-maitresse|Oui.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.</t>
+narrateur|Le poisson orange derrière la plante.
+narrateur|Le mot est déjà là.
+narrateur|Elle avance un peu les lèvres.
+narrateur|La maîtresse verse encore des graines dans le bocal.
+narrateur|Les graines font un tout petit bruit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>pas,eau</t>
+          <t>eau,pas</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Anaïs veut parler. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1451,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle lève la main et elle attend. Que fait Anaïs ?</t>
+          <t>Elle lève la main et elle attend. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1576,7 +1565,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a levé la main. Elle a attendu. Puis parler, c'était son tour. Tu as levé la main. Bravo. Tu as attendu. Puis tu as parlé.</t>
+          <t>Mila lève la main. Elle attend, la main haute. Le poisson passe encore derrière la plante. Mila le suit des yeux. Sa main ne descend pas. Mila, c'est toi. Tu peux parler. Le poisson du bocal est orange. Il se cache derrière la plante. Il nage tout doucement. Derrière la plante, oui. On voit juste sa queue. Merci, Mila. Plus tard, Mila a encore une idée. Les poissons en papier bougent au plafond. Elle lève la main. Elle attend. Mila, c'est encore toi. Les poissons en papier nagent aussi, un peu. Oui. Le crayon bleu glisse dans sa main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anaïs a levé la main. Elle a attendu. &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; parler, c'était son tour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila lève la main. Elle attend, la main haute. Le poisson passe encore derrière la plante. Mila le suit des yeux. Sa main ne descend pas. Mila, c'est toi. Tu peux parler. Le poisson du bocal est orange. Il se cache derrière la plante. Il nage tout doucement. Derrière la plante, oui. On voit juste sa queue. Merci, Mila. Plus tard, Mila a encore une idée. Les poissons en papier bougent au plafond. Elle lève la main. Elle attend. Mila, c'est encore toi. Les poissons en papier nagent aussi, un peu. Oui. Le crayon bleu glisse dans sa main.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,16 +1733,34 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a levé la main.
-narrateur|Elle a attendu.
-narrateur|Puis parler, c'était son tour.
-maitresse|Tu as levé la main.
-maitresse|Bravo.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila lève la main.
+narrateur|Elle attend, la main haute.
+narrateur|Le poisson passe encore derrière la plante.
+narrateur|Mila le suit des yeux.
+narrateur|Sa main ne descend pas.
+maitresse|Mila, c'est toi.
+maitresse|Tu peux parler.
+enfant-f|Le poisson du bocal est orange.
+enfant-f|Il se cache derrière la plante.
+enfant-f|Il nage tout doucement.
+maitresse|Derrière la plante, oui.
+enfant-f|On voit juste sa queue.
+maitresse|Merci, Mila.
+narrateur|Plus tard, Mila a encore une idée.
+narrateur|Les poissons en papier bougent au plafond.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maitresse|Mila, c'est encore toi.
+enfant-f|Les poissons en papier nagent aussi, un peu.
+maitresse|Oui.
+narrateur|Le crayon bleu glisse dans sa main.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1779,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé du poisson ? Oui. Il est orange. Bravo, Mila. Tu as fait du bon travail. Le brouillard est parti. On rentre. La vitre de la cuisine est sèche. La petite maison du doigt n'est plus là.</t>
+          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? Le poisson était derrière la plante. J'ai parlé de lui. Il était orange ? Oui. On voyait sa queue. On rentre. Le brouillard est parti. La vitre de la cuisine est sèche. Mila pose le crayon bleu sur la table. Je le dessine. La plante, aussi ? Oui. Et sa queue. Je te tiens la feuille.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Anaïs range son cartable. Maman l'attend à la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? Le poisson était derrière la plante. J'ai parlé de lui. Il était orange ? Oui. On voyait sa queue. On rentre. Le brouillard est parti. La vitre de la cuisine est sèche. Mila pose le crayon bleu sur la table. Je le dessine. La plante, aussi ? Oui. Et sa queue. Je te tiens la feuille.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,18 +1925,20 @@
 narrateur|Le crayon bleu est encore dans sa poche.
 narrateur|La porte s'ouvre.
 maman|Tu as passé un bon moment ?
-enfant-f|J'ai levé la main.
-enfant-f|J'ai su attendre.
-enfant-f|Puis parler, c'était mon tour.
-papa|Tu as parlé du poisson ?
+enfant-f|Le poisson était derrière la plante.
+enfant-f|J'ai parlé de lui.
+papa|Il était orange ?
 enfant-f|Oui.
-enfant-f|Il est orange.
-maman|Bravo, Mila.
-maman|Tu as fait du bon travail.
+enfant-f|On voyait sa queue.
+maman|On rentre.
 papa|Le brouillard est parti.
-papa|On rentre.
 narrateur|La vitre de la cuisine est sèche.
-narrateur|La petite maison du doigt n'est plus là.</t>
+narrateur|Mila pose le crayon bleu sur la table.
+enfant-f|Je le dessine.
+maman|La plante, aussi ?
+enfant-f|Oui.
+enfant-f|Et sa queue.
+papa|Je te tiens la feuille.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1962,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les bottes rouges sèchent sur le paillasson. Tu as attendu. Puis tu as parlé. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,14 +2110,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Les bottes rouges sèchent sur le paillasson.
-papa|Tu as attendu.
-papa|Puis tu as parlé.
+          <t>narrateur|Le poisson orange est sur la feuille.
+narrateur|La plante aussi, un peu de travers.
+papa|On voit bien sa queue.
 maman|Bonne soirée, ma grande.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2201,6 +2208,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,8 +2113,7 @@
           <t>narrateur|Le poisson orange est sur la feuille.
 narrateur|La plante aussi, un peu de travers.
 papa|On voit bien sa queue.
-maman|Bonne soirée, ma grande.
-narrateur|L'histoire est finie.</t>
+maman|Bonne soirée, ma grande.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2212,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-09.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-09.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le poisson derrière la plante</t>
+          <t>Le poisson orange de Mila</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour à l'arrosoir, puis classe au bocal</t>
+          <t>cuisine à la vitre embuée, classe au bocal, puis table</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mila, papa, maman, maîtresse</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut revoir le poisson orange derrière la plante. Le mot est déjà là. Elle lève la main, elle attend, puis elle parle.</t>
+          <t>Mila veut dire le poisson orange. Un éclat de poisson brille sur l'écaille. Elle coupe papa : les mots se perdent. À l'école, une voix trop près ; elle coupe, trop vite. Elle refuse de foncer, attend, raconte. Merci vécu. L'éclat de poisson tient l'orange.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir de la cour a une goutte au bec. La goutte tombe sur la dalle. Un petit serpent d'eau brille, puis s'arrête. Le yaourt de Mila a un fil de miel. Le miel fait un pont, tu vois ? Il est tout doré. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est derrière ton oreille. Tu l'as senti ? Oui. Il est lisse. Tu voulais revoir le poisson, ce matin. Celui qui se cache. Derrière la plante. Tu le raconteras, si tu veux. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste derrière son oreille. Le poisson du bocal fait un petit tour. Il passe derrière la plante verte. Il est encore là. Bonjour. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson orange derrière la plante. Le mot est déjà là. Elle avance un peu les lèvres. La maîtresse verse encore des graines dans le bocal. Les graines font un tout petit bruit.</t>
+          <t>La vitre de la cuisine est embuée. Le blanc est tiède sous la paume. Mila dessine une petite maison du bout du doigt. Une goutte glisse sur le toit dessiné. Elle a une fenêtre ronde ! Tu as fait le toit, toi ? Oui, et une porte. À côté, Mila dessine un poisson. Le poisson est petit, un peu tordu. Sur une écaille, un éclat de poisson brille. Il brille, papa ! Tu le vois, toi ? Oui, près de la queue. Ça sent le lait tiède, près du bol. Une fumée fine danse au-dessus. Le poisson est orange, dans ma tête. Je veux le dire à l'école. On part après le bol ? Maintenant ! En ce moment, Mila coupe la phrase de papa. Il a une queue, près du toit ! Les deux voix se cognent. Tu disais, Mila ? Le poisson. Personne n'a la phrase entière. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa s'accroupit à la même hauteur. Tu veux parler, ou regarder la goutte ? Parler. Tes bottes rouges attendent sur le paillasson. Les bottes sont un peu froides. On les enfile ? Oui. Une. Puis l'autre. Le crayon bleu est dans ta poche. Tu l'as senti ? Oui. Il est lisse. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main ? Oui, papa. Au revoir, Mila. Au revoir, maman. Plus tard, l'école sent la craie. Dans la classe, des poissons en papier pendent. Ils bougent un peu, au plafond. Un bocal rond brille près du mur. Bonjour. Bonjour, maîtresse. Mila s'assoit sur le tapis rond. Le tapis est un peu frais sous les genoux. Le poisson du bocal fait un petit tour. Il est orange, comme le dessin. C'est le même ! Les mots lui chatouillent la bouche. Elle veut le dire, ce poisson, maintenant. Une voix s'approche, trop près. La voix veut le poisson, elle aussi. Attends, je dois parler ! Ses mots se cognent à la voix. Mila referme la bouche. Les mains restent à plat sur ses genoux. Je veux parler du poisson orange.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir de la cour a une goutte au bec. La goutte tombe sur la dalle. Un petit serpent d'eau brille, puis s'arrête. Le yaourt de Mila a un fil de miel. Le miel fait un pont, tu vois ? Il est tout doré. Tes bottes rouges attendent sur le paillasson. Elles sont un peu froides. On les enfile. Une. Puis l'autre. Le crayon bleu est derrière ton oreille. Tu l'as senti ? Oui. Il est lisse. Tu voulais revoir le poisson, ce matin. Celui qui se cache. Derrière la plante. Tu le raconteras, si tu veux. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main. Le chemin est encore gris. Dans la classe, des poissons en papier pendent. Ils bougent un peu, tout doucement. Un bocal rond brille près de la fenêtre. Le tapis rond est à ta place, Mila. Au revoir. On revient te chercher. Au revoir, maman. Tu poses le sac près du mur. En ce moment, Mila s'assoit sur le tapis rond. Le crayon bleu reste derrière son oreille. Le poisson du bocal fait un petit tour. Il passe derrière la plante verte. Il est encore là. Bonjour. Bonjour. Qui a vu quelque chose qui nage ? Mila a une idée. Le poisson orange derrière la plante. Le mot est déjà là. Elle avance un peu les lèvres. La maîtresse verse encore des graines dans le bocal. Les graines font un tout petit bruit.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vitre de la cuisine est embuée. Le blanc est tiède sous la paume. Mila dessine une petite maison du bout du doigt. Une goutte glisse sur le toit dessiné. Elle a une fenêtre ronde ! Tu as fait le toit, toi ? Oui, et une porte. À côté, Mila dessine un poisson. Le poisson est petit, un peu tordu. Sur une écaille, un &lt;emphasis level="moderate"&gt;éclat de poisson&lt;/emphasis&gt; brille. Il brille, papa ! Tu le vois, toi ? Oui, près de la queue. Ça sent le lait tiède, près du bol. Une fumée fine danse au-dessus. Le poisson est orange, dans ma tête. Je veux le dire à l'école. On part après le bol ? Maintenant ! En ce moment, Mila coupe la phrase de papa. Il a une queue, près du toit ! Les deux voix se cognent. Tu disais, Mila ? Le poisson. Personne n'a la phrase entière. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa s'accroupit à la même hauteur. Tu veux parler, ou regarder la goutte ? Parler. Tes bottes rouges attendent sur le paillasson. Les bottes sont un peu froides. On les enfile ? Oui. Une. Puis l'autre. Le crayon bleu est dans ta poche. Tu l'as senti ? Oui. Il est lisse. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main ? Oui, papa. Au revoir, Mila. Au revoir, maman. Plus tard, l'école sent la craie. Dans la classe, des poissons en papier pendent. Ils bougent un peu, au plafond. Un bocal rond brille près du mur. Bonjour. Bonjour, maîtresse. Mila s'assoit sur le tapis rond. Le tapis est un peu frais sous les genoux. Le poisson du bocal fait un petit tour. Il est orange, comme le dessin. C'est le même ! Les mots lui chatouillent la bouche. Elle veut le dire, ce poisson, maintenant. Une voix s'approche, trop près. La voix veut le poisson, elle aussi. Attends, je dois parler ! Ses mots se cognent à la voix. Mila referme la bouche. Les mains restent à plat sur ses genoux. Je veux parler du poisson orange.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Anaïs arrive en classe avec maman. Maman dit au revoir. Anaïs s'assoit sur le tapis. La maîtresse pose une question. Anaïs a une idée. Elle lève la main. Il faut &lt;emphasis&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Anaïs attend encore. Puis la maîtresse dit : Anaïs, c'est ton tour. Anaïs parle. Elle dit : le chat est gris. La maîtresse sourit. Plus tard, Anaïs a encore une idée. Elle lève la main. Elle attend. Puis elle peut parler. Le soir, maman demande. Anaïs dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. [pause]</t>
+          <t>La vitre de la cuisine est embuée. Le blanc est tiède sous la paume. Mila dessine une petite maison du bout du doigt. Une goutte glisse sur le toit dessiné. Elle a une fenêtre ronde ! Tu as fait le toit, toi ? Oui, et une porte. À côté, Mila dessine un poisson. Le poisson est petit, un peu tordu. Sur une écaille, un &lt;emphasis&gt;éclat de poisson&lt;/emphasis&gt; brille. Il brille, papa ! Tu le vois, toi ? Oui, près de la queue. Ça sent le lait tiède, près du bol. Une fumée fine danse au-dessus. Le poisson est orange, dans ma tête. Je veux le dire à l'école. On part après le bol ? Maintenant ! En ce moment, Mila coupe la phrase de papa. Il a une queue, près du toit ! Les deux voix se cognent. Tu disais, Mila ? Le poisson. Personne n'a la phrase entière. Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Papa s'accroupit à la même hauteur. Tu veux parler, ou regarder la goutte ? Parler. Tes bottes rouges attendent sur le paillasson. Les bottes sont un peu froides. On les enfile ? Oui. Une. Puis l'autre. Le crayon bleu est dans ta poche. Tu l'as senti ? Oui. Il est lisse. Dehors, le brouillard sent l'herbe mouillée. Les bottes font un bruit mou sur le chemin. On tient la main ? Oui, papa. Au revoir, Mila. Au revoir, maman. Plus tard, l'école sent la craie. Dans la classe, des poissons en papier pendent. Ils bougent un peu, au plafond. Un bocal rond brille près du mur. Bonjour. Bonjour, maîtresse. Mila s'assoit sur le tapis rond. Le tapis est un peu frais sous les genoux. Le poisson du bocal fait un petit tour. Il est orange, comme le dessin. C'est le même ! Les mots lui chatouillent la bouche. Elle veut le dire, ce poisson, maintenant. Une voix s'approche, trop près. La voix veut le poisson, elle aussi. Attends, je dois parler ! Ses mots se cognent à la voix. Mila referme la bouche. Les mains restent à plat sur ses genoux. Je veux parler du poisson orange. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>éclat de poisson</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,59 +1326,84 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse; intensite=2; destinataire=enfant; sous_texte=l_eclat_de_poisson_sur_l_ecaille; tempo=naturel; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|L'arrosoir de la cour a une goutte au bec.
-narrateur|La goutte tombe sur la dalle.
-narrateur|Un petit serpent d'eau brille, puis s'arrête.
-narrateur|Le yaourt de Mila a un fil de miel.
-maman|Le miel fait un pont, tu vois ?
-enfant-f|Il est tout doré.
-papa|Tes bottes rouges attendent sur le paillasson.
-papa|Elles sont un peu froides.
-enfant-f|On les enfile.
+          <t>narrateur|La vitre de la cuisine est embuée.
+narrateur|Le blanc est tiède sous la paume.
+narrateur|Mila dessine une petite maison du bout du doigt.
+narrateur|Une goutte glisse sur le toit dessiné.
+enfant-f|Elle a une fenêtre ronde !
+maman|Tu as fait le toit, toi ?
+enfant-f|Oui, et une porte.
+narrateur|À côté, Mila dessine un poisson.
+narrateur|Le poisson est petit, un peu tordu.
+narrateur|Sur une écaille, un éclat de poisson brille.
+enfant-f|Il brille, papa !
+papa|Tu le vois, toi ?
+enfant-f|Oui, près de la queue.
+narrateur|Ça sent le lait tiède, près du bol.
+narrateur|Une fumée fine danse au-dessus.
+enfant-f|Le poisson est orange, dans ma tête.
+enfant-f|Je veux le dire à l'école.
+papa|On part après le bol ?
+enfant-f|Maintenant !
+narrateur|En ce moment, Mila coupe la phrase de papa.
+enfant-f|Il a une queue, près du toit !
+narrateur|Les deux voix se cognent.
+papa|Tu disais, Mila ?
+enfant-f|Le poisson.
+narrateur|Personne n'a la phrase entière.
+narrateur|Le sourire de Mila disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu veux parler, ou regarder la goutte ?
+enfant-f|Parler.
+maman|Tes bottes rouges attendent sur le paillasson.
+narrateur|Les bottes sont un peu froides.
+papa|On les enfile ?
+enfant-f|Oui.
 papa|Une.
 papa|Puis l'autre.
-maman|Le crayon bleu est derrière ton oreille.
+maman|Le crayon bleu est dans ta poche.
 maman|Tu l'as senti ?
 enfant-f|Oui.
 enfant-f|Il est lisse.
-papa|Tu voulais revoir le poisson, ce matin.
-enfant-f|Celui qui se cache.
-enfant-f|Derrière la plante.
-maman|Tu le raconteras, si tu veux.
 narrateur|Dehors, le brouillard sent l'herbe mouillée.
 narrateur|Les bottes font un bruit mou sur le chemin.
-papa|On tient la main.
-papa|Le chemin est encore gris.
+papa|On tient la main ?
+enfant-f|Oui, papa.
+maman|Au revoir, Mila.
+enfant-f|Au revoir, maman.
+narrateur|Plus tard, l'école sent la craie.
 narrateur|Dans la classe, des poissons en papier pendent.
-narrateur|Ils bougent un peu, tout doucement.
-narrateur|Un bocal rond brille près de la fenêtre.
-maman|Le tapis rond est à ta place, Mila.
-maman|Au revoir.
-maman|On revient te chercher.
-enfant-f|Au revoir, maman.
-papa|Tu poses le sac près du mur.
-narrateur|En ce moment, Mila s'assoit sur le tapis rond.
-narrateur|Le crayon bleu reste derrière son oreille.
+narrateur|Ils bougent un peu, au plafond.
+narrateur|Un bocal rond brille près du mur.
+maitresse|Bonjour.
+enfant-f|Bonjour, maîtresse.
+narrateur|Mila s'assoit sur le tapis rond.
+narrateur|Le tapis est un peu frais sous les genoux.
 narrateur|Le poisson du bocal fait un petit tour.
-narrateur|Il passe derrière la plante verte.
-enfant-f|Il est encore là.
-maitresse|Bonjour.
-enfant-f|Bonjour.
-maitresse|Qui a vu quelque chose qui nage ?
-narrateur|Mila a une idée.
-narrateur|Le poisson orange derrière la plante.
-narrateur|Le mot est déjà là.
-narrateur|Elle avance un peu les lèvres.
-narrateur|La maîtresse verse encore des graines dans le bocal.
-narrateur|Les graines font un tout petit bruit.</t>
+narrateur|Il est orange, comme le dessin.
+enfant-f|C'est le même !
+narrateur|Les mots lui chatouillent la bouche.
+narrateur|Elle veut le dire, ce poisson, maintenant.
+narrateur|Une voix s'approche, trop près.
+narrateur|La voix veut le poisson, elle aussi.
+enfant-f|Attends, je dois parler !
+narrateur|Ses mots se cognent à la voix.
+narrateur|Mila referme la bouche.
+narrateur|Les mains restent à plat sur ses genoux.
+enfant-f|Je veux parler du poisson orange.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>eau,pas</t>
+          <t>pas,eau</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1435,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila veut parler. Que fait-elle d'abord ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila veut parler. Que fait-elle &lt;emphasis level="moderate"&gt;d'abord&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Anaïs veut parler. Que fait-elle d'abord ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila veut parler. Que fait-elle &lt;emphasis&gt;d'abord&lt;/emphasis&gt; ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1440,7 +1465,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle lève la main et elle attend. Que fait Mila ?</t>
+          <t>Personne ne l'entend. Que fait Mila d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1478,7 +1503,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1514,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,34 +1529,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>d'abord</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1546,17 +1575,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_attend_avant_de_parler; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1589,17 +1618,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila lève la main. Elle attend, la main haute. Le poisson passe encore derrière la plante. Mila le suit des yeux. Sa main ne descend pas. Mila, c'est toi. Tu peux parler. Le poisson du bocal est orange. Il se cache derrière la plante. Il nage tout doucement. Derrière la plante, oui. On voit juste sa queue. Merci, Mila. Plus tard, Mila a encore une idée. Les poissons en papier bougent au plafond. Elle lève la main. Elle attend. Mila, c'est encore toi. Les poissons en papier nagent aussi, un peu. Oui. Le crayon bleu glisse dans sa main.</t>
+          <t>Mila lève la main. Sa main reste en l'air. Les doigts tremblent un peu. Une autre voix parle d'abord. On entend parler d'une barque en papier. Mila garde la main levée. Mila ? Mila parle. Le poisson du bocal est orange. Comme le dessin de la maison. Les mots arrivent entiers, cette fois. Sur le flanc, l'éclat de poisson tient. Le soir, les assiettes sont chaudes. Ça sent le gratin. La nappe a des petits carreaux. Alors, Mila ? Mila sent l'envie revenir. Elle lève la main, même à table. Papa écoute maman d'abord. Le gratin est prêt. Mila attend que le silence arrive. Elle pose l'autre main sur la nappe. Mila, c'est toi. Le poisson de l'école est le même. Il nage dans le bocal. Merci de nous le dire, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Tu as soif ? Un peu. Mila prend une gorgée. L'eau chante contre le verre. C'est frais.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila lève la main. Elle attend, la main haute. Le poisson passe encore derrière la plante. Mila le suit des yeux. Sa main ne descend pas. Mila, c'est toi. Tu peux parler. Le poisson du bocal est orange. Il se cache derrière la plante. Il nage tout doucement. Derrière la plante, oui. On voit juste sa queue. Merci, Mila. Plus tard, Mila a encore une idée. Les poissons en papier bougent au plafond. Elle lève la main. Elle attend. Mila, c'est encore toi. Les poissons en papier nagent aussi, un peu. Oui. Le crayon bleu glisse dans sa main.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila lève la main. Sa main reste en l'air. Les doigts tremblent un peu. Une autre voix parle d'abord. On entend parler d'une barque en papier. Mila garde la main levée. Mila ? Mila parle. Le poisson du bocal est orange. Comme le dessin de la maison. Les mots arrivent entiers, cette fois. Sur le flanc, l'&lt;emphasis level="moderate"&gt;éclat de poisson&lt;/emphasis&gt; tient. Le soir, les assiettes sont chaudes. Ça sent le gratin. La nappe a des petits carreaux. Alors, Mila ? Mila sent l'envie revenir. Elle lève la main, même à table. Papa écoute maman d'abord. Le gratin est prêt. Mila attend que le silence arrive. Elle pose l'autre main sur la nappe. Mila, c'est toi. Le poisson de l'école est le même. Il nage dans le bocal. Merci de nous le dire, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Tu as soif ? Un peu. Mila prend une gorgée. L'eau chante contre le verre. C'est frais.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Anaïs a levé la main. Elle a attendu. &lt;emphasis&gt;puis&lt;/emphasis&gt; parler, c'était son tour. [pause]</t>
+          <t>Mila lève la main. Sa main reste en l'air. Les doigts tremblent un peu. Une autre voix parle d'abord. On entend parler d'une barque en papier. Mila garde la main levée. Mila ? Mila parle. Le poisson du bocal est orange. Comme le dessin de la maison. Les mots arrivent entiers, cette fois. Sur le flanc, l'&lt;emphasis&gt;éclat de poisson&lt;/emphasis&gt; tient. Le soir, les assiettes sont chaudes. Ça sent le gratin. La nappe a des petits carreaux. Alors, Mila ? Mila sent l'envie revenir. Elle lève la main, même à table. Papa écoute maman d'abord. Le gratin est prêt. Mila attend que le silence arrive. Elle pose l'autre main sur la nappe. Mila, c'est toi. Le poisson de l'école est le même. Il nage dans le bocal. Merci de nous le dire, Mila. Papa a entendu toute la phrase. Le ventre de Mila se desserre. Tu as soif ? Un peu. Mila prend une gorgée. L'eau chante contre le verre. C'est frais. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1646,7 +1675,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1654,10 +1683,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,30 +1709,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>puis</t>
+          <t>éclat de poisson</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1712,10 +1741,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1728,32 +1757,44 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_attend_puis_on_l_entend; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Mila lève la main.
-narrateur|Elle attend, la main haute.
-narrateur|Le poisson passe encore derrière la plante.
-narrateur|Mila le suit des yeux.
-narrateur|Sa main ne descend pas.
-maitresse|Mila, c'est toi.
-maitresse|Tu peux parler.
+narrateur|Sa main reste en l'air.
+narrateur|Les doigts tremblent un peu.
+narrateur|Une autre voix parle d'abord.
+narrateur|On entend parler d'une barque en papier.
+narrateur|Mila garde la main levée.
+maitresse|Mila ?
+narrateur|Mila parle.
 enfant-f|Le poisson du bocal est orange.
-enfant-f|Il se cache derrière la plante.
-enfant-f|Il nage tout doucement.
-maitresse|Derrière la plante, oui.
-enfant-f|On voit juste sa queue.
-maitresse|Merci, Mila.
-narrateur|Plus tard, Mila a encore une idée.
-narrateur|Les poissons en papier bougent au plafond.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-maitresse|Mila, c'est encore toi.
-enfant-f|Les poissons en papier nagent aussi, un peu.
-maitresse|Oui.
-narrateur|Le crayon bleu glisse dans sa main.</t>
+enfant-f|Comme le dessin de la maison.
+narrateur|Les mots arrivent entiers, cette fois.
+narrateur|Sur le flanc, l'éclat de poisson tient.
+narrateur|Le soir, les assiettes sont chaudes.
+narrateur|Ça sent le gratin.
+narrateur|La nappe a des petits carreaux.
+papa|Alors, Mila ?
+narrateur|Mila sent l'envie revenir.
+narrateur|Elle lève la main, même à table.
+narrateur|Papa écoute maman d'abord.
+maman|Le gratin est prêt.
+narrateur|Mila attend que le silence arrive.
+narrateur|Elle pose l'autre main sur la nappe.
+papa|Mila, c'est toi.
+enfant-f|Le poisson de l'école est le même.
+enfant-f|Il nage dans le bocal.
+maman|Merci de nous le dire, Mila.
+narrateur|Papa a entendu toute la phrase.
+narrateur|Le ventre de Mila se desserre.
+papa|Tu as soif ?
+enfant-f|Un peu.
+narrateur|Mila prend une gorgée.
+narrateur|L'eau chante contre le verre.
+enfant-f|C'est frais.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1785,17 +1826,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? Le poisson était derrière la plante. J'ai parlé de lui. Il était orange ? Oui. On voyait sa queue. On rentre. Le brouillard est parti. La vitre de la cuisine est sèche. Mila pose le crayon bleu sur la table. Je le dessine. La plante, aussi ? Oui. Et sa queue. Je te tiens la feuille.</t>
+          <t>Mila glisse de la chaise. Le poisson, je le montre ! Elle court vers la vitre de la cuisine. Elle frotte d'un grand geste. La maison du doigt disparaît. L'éclat de poisson n'est plus là. Il est parti ! Le sourire tremble. Tu le cherches ? Oui. Mila refuse de foncer. Elle reste près de la vitre. Personne ne parle. Ses doigts attendent sur le bois. Elle souffle sur le verre. Un rideau blanc revient, minuscule. Elle dessine la maison, sans se presser. Puis le poisson, près du toit. Comme ce matin ! Tu le vois, toi ? Mila pose un doigt, sans frotter. L'éclat de poisson saute près de la queue. Il est revenu. Il m'a attendue. La table garde le gratin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Mila range son cartable. Le crayon bleu est encore dans sa poche. La porte s'ouvre. Tu as passé un bon moment ? Le poisson était derrière la plante. J'ai parlé de lui. Il était orange ? Oui. On voyait sa queue. On rentre. Le brouillard est parti. La vitre de la cuisine est sèche. Mila pose le crayon bleu sur la table. Je le dessine. La plante, aussi ? Oui. Et sa queue. Je te tiens la feuille.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila glisse de la chaise. Le poisson, je le montre ! Elle court vers la vitre de la cuisine. Elle frotte d'un grand geste. La maison du doigt disparaît. L'&lt;emphasis level="moderate"&gt;éclat de poisson&lt;/emphasis&gt; n'est plus là. Il est parti ! Le sourire tremble. Tu le cherches ? Oui. Mila refuse de foncer. Elle reste près de la vitre. Personne ne parle. Ses doigts attendent sur le bois. Elle souffle sur le verre. Un rideau blanc revient, minuscule. Elle dessine la maison, sans se presser. Puis le poisson, près du toit. Comme ce matin ! Tu le vois, toi ? Mila pose un doigt, sans frotter. L'éclat de poisson saute près de la queue. Il est revenu. Il m'a attendue. La table garde le gratin.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Anaïs range son cartable. Maman l'attend à la porte. [pause]</t>
+          <t>&lt;low-pitch&gt;Mila glisse de la chaise. Le poisson, je le montre ! Elle court vers la vitre de la cuisine. Elle frotte d'un grand geste. La maison du doigt disparaît. L'&lt;emphasis&gt;éclat de poisson&lt;/emphasis&gt; n'est plus là. Il est parti ! Le sourire tremble. Tu le cherches ? Oui. Mila refuse de foncer. Elle reste près de la vitre. Personne ne parle. Ses doigts attendent sur le bois. Elle souffle sur le verre. Un rideau blanc revient, minuscule. Elle dessine la maison, sans se presser. Puis le poisson, près du toit. Comme ce matin ! Tu le vois, toi ? Mila pose un doigt, sans frotter. L'éclat de poisson saute près de la queue. Il est revenu. Il m'a attendue. La table garde le gratin.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1842,7 +1883,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1850,22 +1891,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1874,28 +1919,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de poisson</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1904,41 +1953,52 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=deux_envies_qui_se_heurtent; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat_de_poisson; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Mila range son cartable.
-narrateur|Le crayon bleu est encore dans sa poche.
-narrateur|La porte s'ouvre.
-maman|Tu as passé un bon moment ?
-enfant-f|Le poisson était derrière la plante.
-enfant-f|J'ai parlé de lui.
-papa|Il était orange ?
+          <t>narrateur|Mila glisse de la chaise.
+enfant-f|Le poisson, je le montre !
+narrateur|Elle court vers la vitre de la cuisine.
+narrateur|Elle frotte d'un grand geste.
+narrateur|La maison du doigt disparaît.
+narrateur|L'éclat de poisson n'est plus là.
+enfant-f|Il est parti !
+narrateur|Le sourire tremble.
+papa|Tu le cherches ?
 enfant-f|Oui.
-enfant-f|On voyait sa queue.
-maman|On rentre.
-papa|Le brouillard est parti.
-narrateur|La vitre de la cuisine est sèche.
-narrateur|Mila pose le crayon bleu sur la table.
-enfant-f|Je le dessine.
-maman|La plante, aussi ?
-enfant-f|Oui.
-enfant-f|Et sa queue.
-papa|Je te tiens la feuille.</t>
+narrateur|Mila refuse de foncer.
+narrateur|Elle reste près de la vitre.
+narrateur|Personne ne parle.
+narrateur|Ses doigts attendent sur le bois.
+narrateur|Elle souffle sur le verre.
+narrateur|Un rideau blanc revient, minuscule.
+narrateur|Elle dessine la maison, sans se presser.
+narrateur|Puis le poisson, près du toit.
+enfant-f|Comme ce matin !
+maman|Tu le vois, toi ?
+narrateur|Mila pose un doigt, sans frotter.
+narrateur|L'éclat de poisson saute près de la queue.
+papa|Il est revenu.
+enfant-f|Il m'a attendue.
+narrateur|La table garde le gratin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1970,17 +2030,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande.</t>
+          <t>Maman souffle un peu sur la vitre. Le poisson orange les regarde. C'est lui. On reste un peu ? Oui, maman. Mila serre le bol contre elle. Le lait n'est plus tiède. On se dit bonne nuit dans un moment ? Oui, papa. Les bottes rouges sèchent sur le paillasson. Il est là. On le garde des yeux ? Oui. L'éclat de poisson tient l'orange.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le poisson orange est sur la feuille. La plante aussi, un peu de travers. On voit bien sa queue. Bonne soirée, ma grande.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Maman souffle un peu sur la vitre. Le poisson orange les regarde. C'est lui. On reste un peu ? Oui, maman. Mila serre le bol contre elle. Le lait n'est plus tiède. On se dit bonne nuit dans un moment ? Oui, papa. Les bottes rouges sèchent sur le paillasson. Il est là. On le garde des yeux ? Oui. L'&lt;emphasis level="moderate"&gt;éclat de poisson&lt;/emphasis&gt; tient l'orange.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Maman souffle un peu sur la vitre. Le poisson orange les regarde. C'est lui. On reste un peu ? Oui, maman. Mila serre le bol contre elle. Le lait n'est plus tiède. On se dit bonne nuit dans un moment ? Oui, papa. Les bottes rouges sèchent sur le paillasson. Il est là. On le garde des yeux ? Oui. L'&lt;emphasis&gt;éclat de poisson&lt;/emphasis&gt; tient l'orange.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2027,7 +2087,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2035,10 +2095,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2047,12 +2107,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2061,17 +2121,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de poisson</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2080,11 +2144,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2093,27 +2157,41 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_de_poisson_tient_l_orange; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le poisson orange est sur la feuille.
-narrateur|La plante aussi, un peu de travers.
-papa|On voit bien sa queue.
-maman|Bonne soirée, ma grande.</t>
+          <t>narrateur|Maman souffle un peu sur la vitre.
+narrateur|Le poisson orange les regarde.
+enfant-f|C'est lui.
+maman|On reste un peu ?
+enfant-f|Oui, maman.
+narrateur|Mila serre le bol contre elle.
+narrateur|Le lait n'est plus tiède.
+papa|On se dit bonne nuit dans un moment ?
+enfant-f|Oui, papa.
+narrateur|Les bottes rouges sèchent sur le paillasson.
+enfant-f|Il est là.
+maman|On le garde des yeux ?
+enfant-f|Oui.
+narrateur|L'éclat de poisson tient l'orange.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2219,6 +2297,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
